--- a/grupos/2AEM - Estadisticos 20212.xlsx
+++ b/grupos/2AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -185,10 +185,10 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
   </si>
   <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>-1</v>
@@ -986,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -1009,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>-1</v>
@@ -1063,7 +1063,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1086,7 +1086,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -1140,7 +1140,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1163,7 +1163,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -1217,7 +1217,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1240,7 +1240,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>-1</v>
@@ -1294,7 +1294,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1317,7 +1317,7 @@
         <v>10</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>-1</v>
@@ -1371,7 +1371,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1471,7 +1471,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -1525,7 +1525,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1548,7 +1548,7 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>-1</v>
@@ -1602,7 +1602,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1625,7 +1625,7 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>-1</v>
@@ -1679,7 +1679,7 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -1702,7 +1702,7 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>-1</v>
@@ -1756,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1779,7 +1779,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -1833,7 +1833,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>-1</v>
@@ -1910,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -1933,7 +1933,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>-1</v>
@@ -1987,7 +1987,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2218,7 +2218,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2241,7 +2241,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>-1</v>
@@ -2295,7 +2295,7 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2395,7 +2395,7 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>-1</v>
@@ -2449,7 +2449,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2472,7 +2472,7 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>-1</v>
@@ -2526,7 +2526,7 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2549,7 +2549,7 @@
         <v>10</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>-1</v>
@@ -2603,7 +2603,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -2703,7 +2703,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D27">
         <v>-1</v>
@@ -2757,7 +2757,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -2857,7 +2857,7 @@
         <v>9</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>-1</v>
@@ -2911,7 +2911,7 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -2934,7 +2934,7 @@
         <v>8</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>-1</v>
@@ -2988,7 +2988,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -3011,7 +3011,7 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D31">
         <v>-1</v>
@@ -3065,7 +3065,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3088,7 +3088,7 @@
         <v>10</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>-1</v>
@@ -3142,7 +3142,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -3165,7 +3165,7 @@
         <v>10</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>-1</v>
@@ -3219,7 +3219,7 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -3242,7 +3242,7 @@
         <v>10</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>-1</v>
@@ -3296,7 +3296,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>-1</v>
@@ -3319,7 +3319,7 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>-1</v>
@@ -3373,7 +3373,7 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>-1</v>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3537,22 +3537,25 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
+      <c r="H5">
+        <v>7.3</v>
+      </c>
       <c r="I5">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3626,7 +3629,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3707,7 +3710,7 @@
         <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
@@ -3715,22 +3718,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920151</v>
+        <v>21330051920152</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3747,10 +3750,10 @@
         <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3767,50 +3770,50 @@
         <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920152</v>
+        <v>21330051920153</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920152</v>
+        <v>21330051920153</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3827,84 +3830,84 @@
         <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920153</v>
+        <v>21330051920154</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920153</v>
+        <v>21330051920154</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920153</v>
+        <v>21330051920154</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920154</v>
+        <v>21330051920155</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -3915,16 +3918,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920154</v>
+        <v>21330051920155</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -3935,19 +3938,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920154</v>
+        <v>21330051920155</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>55</v>
@@ -3955,116 +3958,116 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920154</v>
+        <v>21330051920156</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920155</v>
+        <v>21330051920156</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920155</v>
+        <v>21330051920156</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920155</v>
+        <v>21330051920156</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920155</v>
+        <v>21330051920156</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920156</v>
+        <v>21330051920157</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -4075,16 +4078,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920156</v>
+        <v>21330051920157</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -4095,19 +4098,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920156</v>
+        <v>21330051920157</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>55</v>
@@ -4115,136 +4118,136 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920156</v>
+        <v>21330051920158</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920156</v>
+        <v>21330051920158</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920157</v>
+        <v>21330051920158</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920157</v>
+        <v>21330051920159</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920157</v>
+        <v>21330051920159</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920157</v>
+        <v>21330051920159</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920158</v>
+        <v>21330051920160</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -4255,16 +4258,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920158</v>
+        <v>21330051920160</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
@@ -4275,19 +4278,19 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920158</v>
+        <v>21330051920160</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
         <v>55</v>
@@ -4295,196 +4298,196 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920158</v>
+        <v>21330051920161</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920159</v>
+        <v>21330051920161</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920159</v>
+        <v>21330051920161</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920159</v>
+        <v>21330051920162</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E37" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920159</v>
+        <v>21330051920162</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920160</v>
+        <v>21330051920162</v>
       </c>
       <c r="B39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" t="s">
         <v>72</v>
       </c>
-      <c r="C39" t="s">
-        <v>65</v>
-      </c>
       <c r="D39" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920160</v>
+        <v>21330051920163</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920160</v>
+        <v>21330051920163</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C41" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="D41" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920160</v>
+        <v>21330051920163</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="D42" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920161</v>
+        <v>21330051920164</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D43" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
@@ -4495,16 +4498,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920161</v>
+        <v>21330051920164</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D44" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E44" t="s">
         <v>7</v>
@@ -4515,56 +4518,56 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920161</v>
+        <v>21330051920164</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D45" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E45" t="s">
         <v>6</v>
       </c>
       <c r="F45" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920161</v>
+        <v>21330051920164</v>
       </c>
       <c r="B46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920162</v>
+        <v>21330051920165</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D47" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -4575,16 +4578,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920162</v>
+        <v>21330051920165</v>
       </c>
       <c r="B48" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D48" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
@@ -4595,19 +4598,19 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>21330051920162</v>
+        <v>21330051920165</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D49" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E49" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
         <v>55</v>
@@ -4615,79 +4618,79 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>21330051920162</v>
+        <v>21330051920166</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>21330051920163</v>
+        <v>21330051920166</v>
       </c>
       <c r="B51" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>21330051920163</v>
+        <v>21330051920166</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F52" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>21330051920163</v>
+        <v>21330051920166</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D53" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E53" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
         <v>55</v>
@@ -4695,179 +4698,179 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>21330051920163</v>
+        <v>21330051920167</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C54" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D54" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>21330051920164</v>
+        <v>21330051920167</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D55" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E55" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>21330051920164</v>
+        <v>21330051920167</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D56" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E56" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>21330051920164</v>
+        <v>21330051920168</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="D57" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E57" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>21330051920164</v>
+        <v>21330051920168</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="D58" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F58" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>21330051920165</v>
+        <v>21330051920168</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D59" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>21330051920165</v>
+        <v>21330051920169</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C60" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D60" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E60" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>21330051920165</v>
+        <v>21330051920169</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C61" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E61" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>21330051920165</v>
+        <v>21330051920169</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F62" t="s">
         <v>56</v>
@@ -4875,96 +4878,96 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>21330051920166</v>
+        <v>21330051920169</v>
       </c>
       <c r="B63" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="D63" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E63" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>21330051920166</v>
+        <v>21330051920170</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D64" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E64" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F64" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>21330051920166</v>
+        <v>21330051920170</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D65" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E65" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F65" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>21330051920166</v>
+        <v>21330051920170</v>
       </c>
       <c r="B66" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D66" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
       </c>
       <c r="F66" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>21330051920167</v>
+        <v>21330051920171</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D67" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
@@ -4975,16 +4978,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>21330051920167</v>
+        <v>21330051920171</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C68" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D68" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E68" t="s">
         <v>7</v>
@@ -4995,19 +4998,19 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>21330051920167</v>
+        <v>21330051920171</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D69" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E69" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F69" t="s">
         <v>55</v>
@@ -5015,259 +5018,259 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>21330051920167</v>
+        <v>21330051920173</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D70" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F70" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>21330051920168</v>
+        <v>21330051920173</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C71" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="D71" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E71" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F71" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>21330051920168</v>
+        <v>21330051920173</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C72" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="D72" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E72" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F72" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>21330051920168</v>
+        <v>21330051920175</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C73" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D73" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E73" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>21330051920168</v>
+        <v>21330051920175</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D74" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E74" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F74" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>21330051920169</v>
+        <v>21330051920175</v>
       </c>
       <c r="B75" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D75" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E75" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F75" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>21330051920169</v>
+        <v>21330051920175</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="D76" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E76" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>21330051920169</v>
+        <v>21330051920176</v>
       </c>
       <c r="B77" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="D77" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E77" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78">
-        <v>21330051920169</v>
+        <v>21330051920176</v>
       </c>
       <c r="B78" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="D78" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E78" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F78" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>21330051920170</v>
+        <v>21330051920176</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D79" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E79" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F79" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80">
-        <v>21330051920170</v>
+        <v>21330051920177</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D80" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E80" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81">
-        <v>21330051920170</v>
+        <v>21330051920177</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D81" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E81" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F81" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82">
-        <v>21330051920170</v>
+        <v>21330051920177</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D82" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E82" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F82" t="s">
         <v>56</v>
@@ -5275,96 +5278,96 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83">
-        <v>21330051920171</v>
+        <v>21330051920177</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C83" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D83" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E83" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F83" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84">
-        <v>21330051920171</v>
+        <v>21330051920178</v>
       </c>
       <c r="B84" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D84" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E84" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F84" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85">
-        <v>21330051920171</v>
+        <v>21330051920178</v>
       </c>
       <c r="B85" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D85" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E85" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F85" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86">
-        <v>21330051920171</v>
+        <v>21330051920178</v>
       </c>
       <c r="B86" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D86" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87">
-        <v>21330051920173</v>
+        <v>21330051920179</v>
       </c>
       <c r="B87" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D87" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -5375,16 +5378,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88">
-        <v>21330051920173</v>
+        <v>21330051920179</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C88" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D88" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E88" t="s">
         <v>7</v>
@@ -5395,19 +5398,19 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89">
-        <v>21330051920173</v>
+        <v>21330051920179</v>
       </c>
       <c r="B89" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D89" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E89" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F89" t="s">
         <v>55</v>
@@ -5415,196 +5418,196 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90">
-        <v>21330051920173</v>
+        <v>21330051920180</v>
       </c>
       <c r="B90" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="D90" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F90" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91">
-        <v>21330051920175</v>
+        <v>21330051920180</v>
       </c>
       <c r="B91" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C91" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D91" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E91" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F91" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92">
-        <v>21330051920175</v>
+        <v>21330051920180</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C92" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D92" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E92" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F92" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93">
-        <v>21330051920175</v>
+        <v>21330051920181</v>
       </c>
       <c r="B93" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C93" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D93" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E93" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F93" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94">
-        <v>21330051920175</v>
+        <v>21330051920181</v>
       </c>
       <c r="B94" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C94" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D94" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F94" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95">
-        <v>21330051920176</v>
+        <v>21330051920181</v>
       </c>
       <c r="B95" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C95" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D95" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E95" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F95" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96">
-        <v>21330051920176</v>
+        <v>21330051920182</v>
       </c>
       <c r="B96" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C96" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D96" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E96" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97">
-        <v>21330051920176</v>
+        <v>21330051920182</v>
       </c>
       <c r="B97" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C97" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D97" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E97" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F97" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98">
-        <v>21330051920176</v>
+        <v>21330051920182</v>
       </c>
       <c r="B98" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C98" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="D98" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
       </c>
       <c r="F98" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99">
-        <v>21330051920177</v>
+        <v>21330051920183</v>
       </c>
       <c r="B99" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C99" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
@@ -5615,16 +5618,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100">
-        <v>21330051920177</v>
+        <v>21330051920183</v>
       </c>
       <c r="B100" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C100" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E100" t="s">
         <v>7</v>
@@ -5635,19 +5638,19 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101">
-        <v>21330051920177</v>
+        <v>21330051920183</v>
       </c>
       <c r="B101" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C101" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="D101" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E101" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F101" t="s">
         <v>55</v>
@@ -5655,582 +5658,62 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102">
-        <v>21330051920177</v>
+        <v>21330051920184</v>
       </c>
       <c r="B102" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C102" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="D102" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="E102" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F102" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103">
-        <v>21330051920178</v>
+        <v>21330051920184</v>
       </c>
       <c r="B103" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C103" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D103" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="E103" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F103" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104">
-        <v>21330051920178</v>
+        <v>21330051920184</v>
       </c>
       <c r="B104" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C104" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D104" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="E104" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F104" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>21330051920178</v>
-      </c>
-      <c r="B105" t="s">
-        <v>86</v>
-      </c>
-      <c r="C105" t="s">
-        <v>108</v>
-      </c>
-      <c r="D105" t="s">
-        <v>137</v>
-      </c>
-      <c r="E105" t="s">
-        <v>6</v>
-      </c>
-      <c r="F105" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>21330051920178</v>
-      </c>
-      <c r="B106" t="s">
-        <v>86</v>
-      </c>
-      <c r="C106" t="s">
-        <v>108</v>
-      </c>
-      <c r="D106" t="s">
-        <v>137</v>
-      </c>
-      <c r="E106" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>21330051920179</v>
-      </c>
-      <c r="B107" t="s">
-        <v>87</v>
-      </c>
-      <c r="C107" t="s">
-        <v>109</v>
-      </c>
-      <c r="D107" t="s">
-        <v>138</v>
-      </c>
-      <c r="E107" t="s">
-        <v>9</v>
-      </c>
-      <c r="F107" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>21330051920179</v>
-      </c>
-      <c r="B108" t="s">
-        <v>87</v>
-      </c>
-      <c r="C108" t="s">
-        <v>109</v>
-      </c>
-      <c r="D108" t="s">
-        <v>138</v>
-      </c>
-      <c r="E108" t="s">
-        <v>7</v>
-      </c>
-      <c r="F108" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>21330051920179</v>
-      </c>
-      <c r="B109" t="s">
-        <v>87</v>
-      </c>
-      <c r="C109" t="s">
-        <v>109</v>
-      </c>
-      <c r="D109" t="s">
-        <v>138</v>
-      </c>
-      <c r="E109" t="s">
-        <v>6</v>
-      </c>
-      <c r="F109" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>21330051920179</v>
-      </c>
-      <c r="B110" t="s">
-        <v>87</v>
-      </c>
-      <c r="C110" t="s">
-        <v>109</v>
-      </c>
-      <c r="D110" t="s">
-        <v>138</v>
-      </c>
-      <c r="E110" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>21330051920180</v>
-      </c>
-      <c r="B111" t="s">
-        <v>88</v>
-      </c>
-      <c r="C111" t="s">
-        <v>71</v>
-      </c>
-      <c r="D111" t="s">
-        <v>139</v>
-      </c>
-      <c r="E111" t="s">
-        <v>9</v>
-      </c>
-      <c r="F111" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>21330051920180</v>
-      </c>
-      <c r="B112" t="s">
-        <v>88</v>
-      </c>
-      <c r="C112" t="s">
-        <v>71</v>
-      </c>
-      <c r="D112" t="s">
-        <v>139</v>
-      </c>
-      <c r="E112" t="s">
-        <v>7</v>
-      </c>
-      <c r="F112" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>21330051920180</v>
-      </c>
-      <c r="B113" t="s">
-        <v>88</v>
-      </c>
-      <c r="C113" t="s">
-        <v>71</v>
-      </c>
-      <c r="D113" t="s">
-        <v>139</v>
-      </c>
-      <c r="E113" t="s">
-        <v>6</v>
-      </c>
-      <c r="F113" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>21330051920180</v>
-      </c>
-      <c r="B114" t="s">
-        <v>88</v>
-      </c>
-      <c r="C114" t="s">
-        <v>71</v>
-      </c>
-      <c r="D114" t="s">
-        <v>139</v>
-      </c>
-      <c r="E114" t="s">
-        <v>10</v>
-      </c>
-      <c r="F114" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>21330051920181</v>
-      </c>
-      <c r="B115" t="s">
-        <v>89</v>
-      </c>
-      <c r="C115" t="s">
-        <v>110</v>
-      </c>
-      <c r="D115" t="s">
-        <v>140</v>
-      </c>
-      <c r="E115" t="s">
-        <v>9</v>
-      </c>
-      <c r="F115" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>21330051920181</v>
-      </c>
-      <c r="B116" t="s">
-        <v>89</v>
-      </c>
-      <c r="C116" t="s">
-        <v>110</v>
-      </c>
-      <c r="D116" t="s">
-        <v>140</v>
-      </c>
-      <c r="E116" t="s">
-        <v>7</v>
-      </c>
-      <c r="F116" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>21330051920181</v>
-      </c>
-      <c r="B117" t="s">
-        <v>89</v>
-      </c>
-      <c r="C117" t="s">
-        <v>110</v>
-      </c>
-      <c r="D117" t="s">
-        <v>140</v>
-      </c>
-      <c r="E117" t="s">
-        <v>6</v>
-      </c>
-      <c r="F117" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>21330051920181</v>
-      </c>
-      <c r="B118" t="s">
-        <v>89</v>
-      </c>
-      <c r="C118" t="s">
-        <v>110</v>
-      </c>
-      <c r="D118" t="s">
-        <v>140</v>
-      </c>
-      <c r="E118" t="s">
-        <v>10</v>
-      </c>
-      <c r="F118" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>21330051920182</v>
-      </c>
-      <c r="B119" t="s">
-        <v>90</v>
-      </c>
-      <c r="C119" t="s">
-        <v>80</v>
-      </c>
-      <c r="D119" t="s">
-        <v>141</v>
-      </c>
-      <c r="E119" t="s">
-        <v>9</v>
-      </c>
-      <c r="F119" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>21330051920182</v>
-      </c>
-      <c r="B120" t="s">
-        <v>90</v>
-      </c>
-      <c r="C120" t="s">
-        <v>80</v>
-      </c>
-      <c r="D120" t="s">
-        <v>141</v>
-      </c>
-      <c r="E120" t="s">
-        <v>7</v>
-      </c>
-      <c r="F120" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>21330051920182</v>
-      </c>
-      <c r="B121" t="s">
-        <v>90</v>
-      </c>
-      <c r="C121" t="s">
-        <v>80</v>
-      </c>
-      <c r="D121" t="s">
-        <v>141</v>
-      </c>
-      <c r="E121" t="s">
-        <v>6</v>
-      </c>
-      <c r="F121" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>21330051920182</v>
-      </c>
-      <c r="B122" t="s">
-        <v>90</v>
-      </c>
-      <c r="C122" t="s">
-        <v>80</v>
-      </c>
-      <c r="D122" t="s">
-        <v>141</v>
-      </c>
-      <c r="E122" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>21330051920183</v>
-      </c>
-      <c r="B123" t="s">
-        <v>90</v>
-      </c>
-      <c r="C123" t="s">
-        <v>111</v>
-      </c>
-      <c r="D123" t="s">
-        <v>127</v>
-      </c>
-      <c r="E123" t="s">
-        <v>9</v>
-      </c>
-      <c r="F123" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>21330051920183</v>
-      </c>
-      <c r="B124" t="s">
-        <v>90</v>
-      </c>
-      <c r="C124" t="s">
-        <v>111</v>
-      </c>
-      <c r="D124" t="s">
-        <v>127</v>
-      </c>
-      <c r="E124" t="s">
-        <v>7</v>
-      </c>
-      <c r="F124" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>21330051920183</v>
-      </c>
-      <c r="B125" t="s">
-        <v>90</v>
-      </c>
-      <c r="C125" t="s">
-        <v>111</v>
-      </c>
-      <c r="D125" t="s">
-        <v>127</v>
-      </c>
-      <c r="E125" t="s">
-        <v>6</v>
-      </c>
-      <c r="F125" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>21330051920183</v>
-      </c>
-      <c r="B126" t="s">
-        <v>90</v>
-      </c>
-      <c r="C126" t="s">
-        <v>111</v>
-      </c>
-      <c r="D126" t="s">
-        <v>127</v>
-      </c>
-      <c r="E126" t="s">
-        <v>10</v>
-      </c>
-      <c r="F126" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>21330051920184</v>
-      </c>
-      <c r="B127" t="s">
-        <v>91</v>
-      </c>
-      <c r="C127" t="s">
-        <v>89</v>
-      </c>
-      <c r="D127" t="s">
-        <v>112</v>
-      </c>
-      <c r="E127" t="s">
-        <v>9</v>
-      </c>
-      <c r="F127" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>21330051920184</v>
-      </c>
-      <c r="B128" t="s">
-        <v>91</v>
-      </c>
-      <c r="C128" t="s">
-        <v>89</v>
-      </c>
-      <c r="D128" t="s">
-        <v>112</v>
-      </c>
-      <c r="E128" t="s">
-        <v>7</v>
-      </c>
-      <c r="F128" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>21330051920184</v>
-      </c>
-      <c r="B129" t="s">
-        <v>91</v>
-      </c>
-      <c r="C129" t="s">
-        <v>89</v>
-      </c>
-      <c r="D129" t="s">
-        <v>112</v>
-      </c>
-      <c r="E129" t="s">
-        <v>6</v>
-      </c>
-      <c r="F129" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>21330051920184</v>
-      </c>
-      <c r="B130" t="s">
-        <v>91</v>
-      </c>
-      <c r="C130" t="s">
-        <v>89</v>
-      </c>
-      <c r="D130" t="s">
-        <v>112</v>
-      </c>
-      <c r="E130" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -6283,16 +5766,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920151</v>
+        <v>21330051920164</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -6300,16 +5783,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920152</v>
+        <v>21330051920166</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -6317,16 +5800,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920153</v>
+        <v>21330051920169</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -6334,16 +5817,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920154</v>
+        <v>21330051920175</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -6351,16 +5834,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920155</v>
+        <v>21330051920177</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -6368,325 +5851,325 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920157</v>
+        <v>21330051920151</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920158</v>
+        <v>21330051920152</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920159</v>
+        <v>21330051920153</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920160</v>
+        <v>21330051920154</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920161</v>
+        <v>21330051920155</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920162</v>
+        <v>21330051920157</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920163</v>
+        <v>21330051920158</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920164</v>
+        <v>21330051920159</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920165</v>
+        <v>21330051920160</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920166</v>
+        <v>21330051920161</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920167</v>
+        <v>21330051920162</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920168</v>
+        <v>21330051920163</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920169</v>
+        <v>21330051920165</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920170</v>
+        <v>21330051920167</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920171</v>
+        <v>21330051920168</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920173</v>
+        <v>21330051920170</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920175</v>
+        <v>21330051920171</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920176</v>
+        <v>21330051920173</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920177</v>
+        <v>21330051920176</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6703,7 +6186,7 @@
         <v>137</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6720,7 +6203,7 @@
         <v>138</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6737,7 +6220,7 @@
         <v>139</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6754,7 +6237,7 @@
         <v>140</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6771,7 +6254,7 @@
         <v>141</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6788,7 +6271,7 @@
         <v>127</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6805,7 +6288,7 @@
         <v>112</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2AEM - Estadisticos 20212.xlsx
+++ b/grupos/2AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -179,24 +179,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
+    <t>Aurioles Maldonado Luis Gustavo</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Aurioles Maldonado Luis Gustavo</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,24 +209,72 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>CHARBEL</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
+    <t>ANGEL FIDEL</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>BAROJAS</t>
   </si>
   <si>
     <t>CUAQUEHUA</t>
   </si>
   <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
     <t>ESPINOSA</t>
   </si>
   <si>
@@ -239,45 +287,27 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>LOYO</t>
-  </si>
-  <si>
     <t>LORENZO</t>
   </si>
   <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
     <t>MAYO</t>
   </si>
   <si>
     <t>MEDINA</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
     <t>MOLOHUA</t>
   </si>
   <si>
     <t>RICO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
     <t>SANDOVAL</t>
   </si>
   <si>
@@ -311,9 +341,6 @@
     <t>TZANAHUA</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -323,24 +350,15 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>ROSETE</t>
   </si>
   <si>
-    <t>NERI</t>
-  </si>
-  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>NIEVES</t>
   </si>
   <si>
@@ -371,9 +389,6 @@
     <t>CARLOS DANIEL</t>
   </si>
   <si>
-    <t>JUAN GERARDO</t>
-  </si>
-  <si>
     <t>ALEXANDER</t>
   </si>
   <si>
@@ -395,24 +410,15 @@
     <t>MIGUEL</t>
   </si>
   <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
     <t>ROBERTO</t>
   </si>
   <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
     <t>LUIS OMAR</t>
   </si>
   <si>
     <t>SALVADOR</t>
   </si>
   <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
     <t>TAURINO</t>
   </si>
   <si>
@@ -422,13 +428,7 @@
     <t>CHRISTIAN GABRIEL</t>
   </si>
   <si>
-    <t>JHOSUA LEVY</t>
-  </si>
-  <si>
     <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>ANGEL FIDEL</t>
   </si>
   <si>
     <t>JONATHAN</t>
@@ -935,16 +935,16 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -989,16 +989,16 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1012,16 +1012,16 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1066,16 +1066,16 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1089,16 +1089,16 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1143,16 +1143,16 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1166,16 +1166,16 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1220,16 +1220,16 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>10</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1243,16 +1243,16 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E8">
         <v>10</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1297,16 +1297,16 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1320,16 +1320,16 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1374,16 +1374,16 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1397,7 +1397,7 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>8</v>
@@ -1406,7 +1406,7 @@
         <v>-1</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1451,7 +1451,7 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1460,7 +1460,7 @@
         <v>-1</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1474,16 +1474,16 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1528,16 +1528,16 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>10</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1551,16 +1551,16 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>10</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1605,16 +1605,16 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1628,16 +1628,16 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E13">
         <v>10</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1682,16 +1682,16 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>10</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1705,16 +1705,16 @@
         <v>8</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1759,16 +1759,16 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1782,16 +1782,16 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>10</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1836,16 +1836,16 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1859,16 +1859,16 @@
         <v>8</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>10</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1913,16 +1913,16 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1936,16 +1936,16 @@
         <v>6</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E17">
         <v>10</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -1990,16 +1990,16 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>10</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2013,16 +2013,16 @@
         <v>-1</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>7</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H18">
         <v>-1</v>
@@ -2067,16 +2067,16 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2090,16 +2090,16 @@
         <v>-1</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>10</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H19">
         <v>-1</v>
@@ -2144,16 +2144,16 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>10</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2167,16 +2167,16 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>10</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2221,16 +2221,16 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2244,16 +2244,16 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>10</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>-1</v>
@@ -2298,16 +2298,16 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>10</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2321,16 +2321,16 @@
         <v>-1</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>10</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2375,16 +2375,16 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>10</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2398,16 +2398,16 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E23">
         <v>10</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2452,16 +2452,16 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>10</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2475,16 +2475,16 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>10</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2529,16 +2529,16 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2552,16 +2552,16 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E25">
         <v>10</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2606,16 +2606,16 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2629,7 +2629,7 @@
         <v>-1</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>10</v>
@@ -2638,7 +2638,7 @@
         <v>-1</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2683,7 +2683,7 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2692,7 +2692,7 @@
         <v>-1</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2706,16 +2706,16 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>10</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2760,16 +2760,16 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2783,7 +2783,7 @@
         <v>-1</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>10</v>
@@ -2792,7 +2792,7 @@
         <v>-1</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2837,7 +2837,7 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2846,7 +2846,7 @@
         <v>-1</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2860,16 +2860,16 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>10</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2914,16 +2914,16 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>10</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2937,16 +2937,16 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -2991,16 +2991,16 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3014,16 +3014,16 @@
         <v>9</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E31">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3068,16 +3068,16 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>10</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3091,16 +3091,16 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E32">
         <v>10</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3145,16 +3145,16 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>10</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3168,16 +3168,16 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E33">
         <v>10</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3222,16 +3222,16 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3245,16 +3245,16 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>10</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3299,16 +3299,16 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>10</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3322,16 +3322,16 @@
         <v>9</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E35">
         <v>10</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3376,16 +3376,16 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>10</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3450,27 +3450,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.3</v>
+      </c>
       <c r="I2">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3479,27 +3482,30 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>8.4</v>
+      </c>
       <c r="I3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3508,27 +3514,30 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>9.5</v>
+      </c>
       <c r="I4">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3537,30 +3546,30 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>81.25</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3569,30 +3578,30 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3613,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3629,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3658,59 +3667,59 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920151</v>
+        <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920151</v>
+        <v>21330051920156</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920151</v>
+        <v>21330051920156</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
@@ -3718,19 +3727,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920152</v>
+        <v>21330051920164</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>53</v>
@@ -3738,1982 +3747,122 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920152</v>
+        <v>21330051920166</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920152</v>
+        <v>21330051920169</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920153</v>
+        <v>21330051920175</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920153</v>
+        <v>21330051920175</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920153</v>
+        <v>21330051920177</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920154</v>
+        <v>21330051920177</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920154</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920154</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920155</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920155</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920155</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920156</v>
-      </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920156</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920156</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920156</v>
-      </c>
-      <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920156</v>
-      </c>
-      <c r="B21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>117</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920157</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920157</v>
-      </c>
-      <c r="B23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920157</v>
-      </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920158</v>
-      </c>
-      <c r="B25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" t="s">
-        <v>119</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920158</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920158</v>
-      </c>
-      <c r="B27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920159</v>
-      </c>
-      <c r="B28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920159</v>
-      </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" t="s">
-        <v>120</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920159</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>120</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920160</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" t="s">
-        <v>121</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920160</v>
-      </c>
-      <c r="B32" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920160</v>
-      </c>
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" t="s">
-        <v>121</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920161</v>
-      </c>
-      <c r="B34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920161</v>
-      </c>
-      <c r="B35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920161</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" t="s">
-        <v>100</v>
-      </c>
-      <c r="D36" t="s">
-        <v>122</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920162</v>
-      </c>
-      <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920162</v>
-      </c>
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" t="s">
-        <v>72</v>
-      </c>
-      <c r="D38" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920162</v>
-      </c>
-      <c r="B39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D39" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920163</v>
-      </c>
-      <c r="B40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" t="s">
-        <v>124</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920163</v>
-      </c>
-      <c r="B41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" t="s">
-        <v>95</v>
-      </c>
-      <c r="D41" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920163</v>
-      </c>
-      <c r="B42" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" t="s">
-        <v>124</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920164</v>
-      </c>
-      <c r="B43" t="s">
-        <v>75</v>
-      </c>
-      <c r="C43" t="s">
-        <v>101</v>
-      </c>
-      <c r="D43" t="s">
-        <v>125</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920164</v>
-      </c>
-      <c r="B44" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" t="s">
-        <v>101</v>
-      </c>
-      <c r="D44" t="s">
-        <v>125</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920164</v>
-      </c>
-      <c r="B45" t="s">
-        <v>75</v>
-      </c>
-      <c r="C45" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920164</v>
-      </c>
-      <c r="B46" t="s">
-        <v>75</v>
-      </c>
-      <c r="C46" t="s">
-        <v>101</v>
-      </c>
-      <c r="D46" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920165</v>
-      </c>
-      <c r="B47" t="s">
-        <v>76</v>
-      </c>
-      <c r="C47" t="s">
-        <v>102</v>
-      </c>
-      <c r="D47" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920165</v>
-      </c>
-      <c r="B48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C48" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920165</v>
-      </c>
-      <c r="B49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" t="s">
-        <v>126</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920166</v>
-      </c>
-      <c r="B50" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" t="s">
-        <v>127</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920166</v>
-      </c>
-      <c r="B51" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" t="s">
-        <v>103</v>
-      </c>
-      <c r="D51" t="s">
-        <v>127</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920166</v>
-      </c>
-      <c r="B52" t="s">
-        <v>77</v>
-      </c>
-      <c r="C52" t="s">
-        <v>103</v>
-      </c>
-      <c r="D52" t="s">
-        <v>127</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920166</v>
-      </c>
-      <c r="B53" t="s">
-        <v>77</v>
-      </c>
-      <c r="C53" t="s">
-        <v>103</v>
-      </c>
-      <c r="D53" t="s">
-        <v>127</v>
-      </c>
-      <c r="E53" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920167</v>
-      </c>
-      <c r="B54" t="s">
-        <v>78</v>
-      </c>
-      <c r="C54" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" t="s">
-        <v>128</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920167</v>
-      </c>
-      <c r="B55" t="s">
-        <v>78</v>
-      </c>
-      <c r="C55" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" t="s">
-        <v>128</v>
-      </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920167</v>
-      </c>
-      <c r="B56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" t="s">
-        <v>104</v>
-      </c>
-      <c r="D56" t="s">
-        <v>128</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920168</v>
-      </c>
-      <c r="B57" t="s">
-        <v>79</v>
-      </c>
-      <c r="C57" t="s">
-        <v>74</v>
-      </c>
-      <c r="D57" t="s">
-        <v>129</v>
-      </c>
-      <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920168</v>
-      </c>
-      <c r="B58" t="s">
-        <v>79</v>
-      </c>
-      <c r="C58" t="s">
-        <v>74</v>
-      </c>
-      <c r="D58" t="s">
-        <v>129</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920168</v>
-      </c>
-      <c r="B59" t="s">
-        <v>79</v>
-      </c>
-      <c r="C59" t="s">
-        <v>74</v>
-      </c>
-      <c r="D59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920169</v>
-      </c>
-      <c r="B60" t="s">
-        <v>80</v>
-      </c>
-      <c r="C60" t="s">
-        <v>73</v>
-      </c>
-      <c r="D60" t="s">
-        <v>130</v>
-      </c>
-      <c r="E60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920169</v>
-      </c>
-      <c r="B61" t="s">
-        <v>80</v>
-      </c>
-      <c r="C61" t="s">
-        <v>73</v>
-      </c>
-      <c r="D61" t="s">
-        <v>130</v>
-      </c>
-      <c r="E61" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920169</v>
-      </c>
-      <c r="B62" t="s">
-        <v>80</v>
-      </c>
-      <c r="C62" t="s">
-        <v>73</v>
-      </c>
-      <c r="D62" t="s">
-        <v>130</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920169</v>
-      </c>
-      <c r="B63" t="s">
-        <v>80</v>
-      </c>
-      <c r="C63" t="s">
-        <v>73</v>
-      </c>
-      <c r="D63" t="s">
-        <v>130</v>
-      </c>
-      <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920170</v>
-      </c>
-      <c r="B64" t="s">
-        <v>80</v>
-      </c>
-      <c r="C64" t="s">
-        <v>91</v>
-      </c>
-      <c r="D64" t="s">
-        <v>131</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920170</v>
-      </c>
-      <c r="B65" t="s">
-        <v>80</v>
-      </c>
-      <c r="C65" t="s">
-        <v>91</v>
-      </c>
-      <c r="D65" t="s">
-        <v>131</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920170</v>
-      </c>
-      <c r="B66" t="s">
-        <v>80</v>
-      </c>
-      <c r="C66" t="s">
-        <v>91</v>
-      </c>
-      <c r="D66" t="s">
-        <v>131</v>
-      </c>
-      <c r="E66" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920171</v>
-      </c>
-      <c r="B67" t="s">
-        <v>81</v>
-      </c>
-      <c r="C67" t="s">
-        <v>80</v>
-      </c>
-      <c r="D67" t="s">
-        <v>132</v>
-      </c>
-      <c r="E67" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920171</v>
-      </c>
-      <c r="B68" t="s">
-        <v>81</v>
-      </c>
-      <c r="C68" t="s">
-        <v>80</v>
-      </c>
-      <c r="D68" t="s">
-        <v>132</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920171</v>
-      </c>
-      <c r="B69" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" t="s">
-        <v>80</v>
-      </c>
-      <c r="D69" t="s">
-        <v>132</v>
-      </c>
-      <c r="E69" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920173</v>
-      </c>
-      <c r="B70" t="s">
-        <v>82</v>
-      </c>
-      <c r="C70" t="s">
-        <v>105</v>
-      </c>
-      <c r="D70" t="s">
-        <v>133</v>
-      </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920173</v>
-      </c>
-      <c r="B71" t="s">
-        <v>82</v>
-      </c>
-      <c r="C71" t="s">
-        <v>105</v>
-      </c>
-      <c r="D71" t="s">
-        <v>133</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920173</v>
-      </c>
-      <c r="B72" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" t="s">
-        <v>105</v>
-      </c>
-      <c r="D72" t="s">
-        <v>133</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920175</v>
-      </c>
-      <c r="B73" t="s">
-        <v>83</v>
-      </c>
-      <c r="C73" t="s">
-        <v>106</v>
-      </c>
-      <c r="D73" t="s">
-        <v>134</v>
-      </c>
-      <c r="E73" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920175</v>
-      </c>
-      <c r="B74" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" t="s">
-        <v>106</v>
-      </c>
-      <c r="D74" t="s">
-        <v>134</v>
-      </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920175</v>
-      </c>
-      <c r="B75" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" t="s">
-        <v>106</v>
-      </c>
-      <c r="D75" t="s">
-        <v>134</v>
-      </c>
-      <c r="E75" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920175</v>
-      </c>
-      <c r="B76" t="s">
-        <v>83</v>
-      </c>
-      <c r="C76" t="s">
-        <v>106</v>
-      </c>
-      <c r="D76" t="s">
-        <v>134</v>
-      </c>
-      <c r="E76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920176</v>
-      </c>
-      <c r="B77" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" t="s">
-        <v>107</v>
-      </c>
-      <c r="D77" t="s">
-        <v>135</v>
-      </c>
-      <c r="E77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920176</v>
-      </c>
-      <c r="B78" t="s">
-        <v>84</v>
-      </c>
-      <c r="C78" t="s">
-        <v>107</v>
-      </c>
-      <c r="D78" t="s">
-        <v>135</v>
-      </c>
-      <c r="E78" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920176</v>
-      </c>
-      <c r="B79" t="s">
-        <v>84</v>
-      </c>
-      <c r="C79" t="s">
-        <v>107</v>
-      </c>
-      <c r="D79" t="s">
-        <v>135</v>
-      </c>
-      <c r="E79" t="s">
-        <v>10</v>
-      </c>
-      <c r="F79" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920177</v>
-      </c>
-      <c r="B80" t="s">
-        <v>85</v>
-      </c>
-      <c r="C80" t="s">
-        <v>65</v>
-      </c>
-      <c r="D80" t="s">
-        <v>136</v>
-      </c>
-      <c r="E80" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920177</v>
-      </c>
-      <c r="B81" t="s">
-        <v>85</v>
-      </c>
-      <c r="C81" t="s">
-        <v>65</v>
-      </c>
-      <c r="D81" t="s">
-        <v>136</v>
-      </c>
-      <c r="E81" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920177</v>
-      </c>
-      <c r="B82" t="s">
-        <v>85</v>
-      </c>
-      <c r="C82" t="s">
-        <v>65</v>
-      </c>
-      <c r="D82" t="s">
-        <v>136</v>
-      </c>
-      <c r="E82" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920177</v>
-      </c>
-      <c r="B83" t="s">
-        <v>85</v>
-      </c>
-      <c r="C83" t="s">
-        <v>65</v>
-      </c>
-      <c r="D83" t="s">
-        <v>136</v>
-      </c>
-      <c r="E83" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920178</v>
-      </c>
-      <c r="B84" t="s">
-        <v>86</v>
-      </c>
-      <c r="C84" t="s">
-        <v>108</v>
-      </c>
-      <c r="D84" t="s">
-        <v>137</v>
-      </c>
-      <c r="E84" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920178</v>
-      </c>
-      <c r="B85" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" t="s">
-        <v>108</v>
-      </c>
-      <c r="D85" t="s">
-        <v>137</v>
-      </c>
-      <c r="E85" t="s">
-        <v>7</v>
-      </c>
-      <c r="F85" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920178</v>
-      </c>
-      <c r="B86" t="s">
-        <v>86</v>
-      </c>
-      <c r="C86" t="s">
-        <v>108</v>
-      </c>
-      <c r="D86" t="s">
-        <v>137</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920179</v>
-      </c>
-      <c r="B87" t="s">
-        <v>87</v>
-      </c>
-      <c r="C87" t="s">
-        <v>109</v>
-      </c>
-      <c r="D87" t="s">
-        <v>138</v>
-      </c>
-      <c r="E87" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920179</v>
-      </c>
-      <c r="B88" t="s">
-        <v>87</v>
-      </c>
-      <c r="C88" t="s">
-        <v>109</v>
-      </c>
-      <c r="D88" t="s">
-        <v>138</v>
-      </c>
-      <c r="E88" t="s">
-        <v>7</v>
-      </c>
-      <c r="F88" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920179</v>
-      </c>
-      <c r="B89" t="s">
-        <v>87</v>
-      </c>
-      <c r="C89" t="s">
-        <v>109</v>
-      </c>
-      <c r="D89" t="s">
-        <v>138</v>
-      </c>
-      <c r="E89" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920180</v>
-      </c>
-      <c r="B90" t="s">
-        <v>88</v>
-      </c>
-      <c r="C90" t="s">
-        <v>71</v>
-      </c>
-      <c r="D90" t="s">
-        <v>139</v>
-      </c>
-      <c r="E90" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>21330051920180</v>
-      </c>
-      <c r="B91" t="s">
-        <v>88</v>
-      </c>
-      <c r="C91" t="s">
-        <v>71</v>
-      </c>
-      <c r="D91" t="s">
-        <v>139</v>
-      </c>
-      <c r="E91" t="s">
-        <v>7</v>
-      </c>
-      <c r="F91" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>21330051920180</v>
-      </c>
-      <c r="B92" t="s">
-        <v>88</v>
-      </c>
-      <c r="C92" t="s">
-        <v>71</v>
-      </c>
-      <c r="D92" t="s">
-        <v>139</v>
-      </c>
-      <c r="E92" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920181</v>
-      </c>
-      <c r="B93" t="s">
-        <v>89</v>
-      </c>
-      <c r="C93" t="s">
-        <v>110</v>
-      </c>
-      <c r="D93" t="s">
-        <v>140</v>
-      </c>
-      <c r="E93" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920181</v>
-      </c>
-      <c r="B94" t="s">
-        <v>89</v>
-      </c>
-      <c r="C94" t="s">
-        <v>110</v>
-      </c>
-      <c r="D94" t="s">
-        <v>140</v>
-      </c>
-      <c r="E94" t="s">
-        <v>7</v>
-      </c>
-      <c r="F94" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>21330051920181</v>
-      </c>
-      <c r="B95" t="s">
-        <v>89</v>
-      </c>
-      <c r="C95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D95" t="s">
-        <v>140</v>
-      </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>21330051920182</v>
-      </c>
-      <c r="B96" t="s">
-        <v>90</v>
-      </c>
-      <c r="C96" t="s">
-        <v>80</v>
-      </c>
-      <c r="D96" t="s">
-        <v>141</v>
-      </c>
-      <c r="E96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>21330051920182</v>
-      </c>
-      <c r="B97" t="s">
-        <v>90</v>
-      </c>
-      <c r="C97" t="s">
-        <v>80</v>
-      </c>
-      <c r="D97" t="s">
-        <v>141</v>
-      </c>
-      <c r="E97" t="s">
-        <v>7</v>
-      </c>
-      <c r="F97" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>21330051920182</v>
-      </c>
-      <c r="B98" t="s">
-        <v>90</v>
-      </c>
-      <c r="C98" t="s">
-        <v>80</v>
-      </c>
-      <c r="D98" t="s">
-        <v>141</v>
-      </c>
-      <c r="E98" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>21330051920183</v>
-      </c>
-      <c r="B99" t="s">
-        <v>90</v>
-      </c>
-      <c r="C99" t="s">
-        <v>111</v>
-      </c>
-      <c r="D99" t="s">
-        <v>127</v>
-      </c>
-      <c r="E99" t="s">
-        <v>9</v>
-      </c>
-      <c r="F99" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>21330051920183</v>
-      </c>
-      <c r="B100" t="s">
-        <v>90</v>
-      </c>
-      <c r="C100" t="s">
-        <v>111</v>
-      </c>
-      <c r="D100" t="s">
-        <v>127</v>
-      </c>
-      <c r="E100" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>21330051920183</v>
-      </c>
-      <c r="B101" t="s">
-        <v>90</v>
-      </c>
-      <c r="C101" t="s">
-        <v>111</v>
-      </c>
-      <c r="D101" t="s">
-        <v>127</v>
-      </c>
-      <c r="E101" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>21330051920184</v>
-      </c>
-      <c r="B102" t="s">
-        <v>91</v>
-      </c>
-      <c r="C102" t="s">
-        <v>89</v>
-      </c>
-      <c r="D102" t="s">
-        <v>112</v>
-      </c>
-      <c r="E102" t="s">
-        <v>9</v>
-      </c>
-      <c r="F102" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>21330051920184</v>
-      </c>
-      <c r="B103" t="s">
-        <v>91</v>
-      </c>
-      <c r="C103" t="s">
-        <v>89</v>
-      </c>
-      <c r="D103" t="s">
-        <v>112</v>
-      </c>
-      <c r="E103" t="s">
-        <v>7</v>
-      </c>
-      <c r="F103" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>21330051920184</v>
-      </c>
-      <c r="B104" t="s">
-        <v>91</v>
-      </c>
-      <c r="C104" t="s">
-        <v>89</v>
-      </c>
-      <c r="D104" t="s">
-        <v>112</v>
-      </c>
-      <c r="E104" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -5752,101 +3901,101 @@
         <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920164</v>
+        <v>21330051920175</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920166</v>
+        <v>21330051920177</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920169</v>
+        <v>21330051920164</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920175</v>
+        <v>21330051920166</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920177</v>
+        <v>21330051920169</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5854,16 +4003,16 @@
         <v>21330051920151</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5871,16 +4020,16 @@
         <v>21330051920152</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5888,16 +4037,16 @@
         <v>21330051920153</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5905,16 +4054,16 @@
         <v>21330051920154</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5922,16 +4071,16 @@
         <v>21330051920155</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5939,16 +4088,16 @@
         <v>21330051920157</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5956,16 +4105,16 @@
         <v>21330051920158</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5973,16 +4122,16 @@
         <v>21330051920159</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5990,16 +4139,16 @@
         <v>21330051920160</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6007,16 +4156,16 @@
         <v>21330051920161</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6024,16 +4173,16 @@
         <v>21330051920162</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6041,16 +4190,16 @@
         <v>21330051920163</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6058,16 +4207,16 @@
         <v>21330051920165</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6075,16 +4224,16 @@
         <v>21330051920167</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6092,16 +4241,16 @@
         <v>21330051920168</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6109,16 +4258,16 @@
         <v>21330051920170</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6126,16 +4275,16 @@
         <v>21330051920171</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6143,16 +4292,16 @@
         <v>21330051920173</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6160,16 +4309,16 @@
         <v>21330051920176</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6177,16 +4326,16 @@
         <v>21330051920178</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
         <v>137</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6194,16 +4343,16 @@
         <v>21330051920179</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
         <v>138</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6211,16 +4360,16 @@
         <v>21330051920180</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
         <v>139</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6228,16 +4377,16 @@
         <v>21330051920181</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>140</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6245,16 +4394,16 @@
         <v>21330051920182</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D31" t="s">
         <v>141</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6262,16 +4411,16 @@
         <v>21330051920183</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6279,16 +4428,16 @@
         <v>21330051920184</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6298,7 +4447,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6328,6 +4477,167 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920175</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920175</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920177</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920177</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920164</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920166</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920169</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2AEM - Estadisticos 20212.xlsx
+++ b/grupos/2AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -185,13 +185,13 @@
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Cruz Alejo José Armando</t>
@@ -947,16 +947,16 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -983,7 +983,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -992,7 +992,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -1024,16 +1024,16 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1101,16 +1101,16 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1178,16 +1178,16 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1220,10 +1220,10 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1255,16 +1255,16 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1332,13 +1332,13 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1374,7 +1374,7 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1391,7 +1391,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>-1</v>
@@ -1409,16 +1409,16 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1445,13 +1445,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1486,16 +1486,16 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1563,16 +1563,16 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1599,13 +1599,13 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>6</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1640,16 +1640,16 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1676,13 +1676,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>7</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1717,16 +1717,16 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1794,13 +1794,13 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1871,13 +1871,13 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1913,7 +1913,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1948,16 +1948,16 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -1984,16 +1984,16 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>6</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2025,16 +2025,16 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2061,13 +2061,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2102,13 +2102,13 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2144,7 +2144,7 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2179,16 +2179,16 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2224,7 +2224,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2256,13 +2256,13 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2292,13 +2292,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>6</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2333,16 +2333,16 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2410,16 +2410,16 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2446,7 +2446,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2455,7 +2455,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2487,16 +2487,16 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2532,7 +2532,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2564,16 +2564,16 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2641,16 +2641,16 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2683,10 +2683,10 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>-1</v>
@@ -2718,13 +2718,13 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2760,7 +2760,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2795,16 +2795,16 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2831,7 +2831,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -2840,7 +2840,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>-1</v>
@@ -2872,16 +2872,16 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2908,13 +2908,13 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>7</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -2949,16 +2949,16 @@
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -2985,13 +2985,13 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>7</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3026,13 +3026,13 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3068,7 +3068,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3103,13 +3103,13 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3139,13 +3139,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>6</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3180,16 +3180,16 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3225,7 +3225,7 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3257,13 +3257,13 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3293,13 +3293,13 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>7</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3334,16 +3334,16 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3514,13 +3514,13 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -3529,15 +3529,15 @@
         <v>9.5</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3558,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3569,7 +3569,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3590,7 +3590,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3638,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3707,36 +3707,36 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920156</v>
+        <v>21330051920164</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920164</v>
+        <v>21330051920166</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -3747,16 +3747,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920166</v>
+        <v>21330051920169</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -3767,22 +3767,22 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920169</v>
+        <v>21330051920175</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3799,30 +3799,30 @@
         <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920175</v>
+        <v>21330051920177</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3839,29 +3839,9 @@
         <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920177</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3910,7 +3890,7 @@
         <v>75</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4447,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4479,16 +4459,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920175</v>
+        <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4502,16 +4482,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920175</v>
+        <v>21330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4525,16 +4505,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920177</v>
+        <v>21330051920175</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4548,16 +4528,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920177</v>
+        <v>21330051920175</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -4571,16 +4551,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920164</v>
+        <v>21330051920177</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4594,22 +4574,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920166</v>
+        <v>21330051920177</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -4617,16 +4597,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920169</v>
+        <v>21330051920164</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4635,6 +4615,52 @@
         <v>53</v>
       </c>
       <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920166</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920169</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2AEM - Estadisticos 20212.xlsx
+++ b/grupos/2AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -209,226 +209,226 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>CUAQUEHUA</t>
+  </si>
+  <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>FERNANDEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>LOYO</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
     <t>MACARIO</t>
   </si>
   <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>SAN JUAN</t>
   </si>
   <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>TERRAZAS</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>VIVAS</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>DIMAS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>NERI</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>AGUILAR</t>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>AMECA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>SAMUEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>CARLOS DANIEL</t>
   </si>
   <si>
     <t>JUAN GERARDO</t>
   </si>
   <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>EVELIN MAYRIN</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>FELIX RAYMUNDO</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>SALVADOR</t>
+  </si>
+  <si>
     <t>CHARBEL</t>
   </si>
   <si>
+    <t>TAURINO</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>CHRISTIAN GABRIEL</t>
+  </si>
+  <si>
     <t>JHOSUA LEVY</t>
   </si>
   <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
     <t>ANGEL FIDEL</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>VIVAS</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DIMAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>SAMUEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>CARLOS DANIEL</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>EVELIN MAYRIN</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>FELIX RAYMUNDO</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>SALVADOR</t>
-  </si>
-  <si>
-    <t>TAURINO</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>CHRISTIAN GABRIEL</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
   </si>
   <si>
     <t>JONATHAN</t>
@@ -950,7 +950,7 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>9</v>
@@ -959,10 +959,10 @@
         <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -986,7 +986,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>10</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -1036,10 +1036,10 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1063,7 +1063,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1075,7 +1075,7 @@
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1104,7 +1104,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1113,10 +1113,10 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1149,10 +1149,10 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1181,7 +1181,7 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -1190,10 +1190,10 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1226,7 +1226,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1258,7 +1258,7 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -1267,10 +1267,10 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1294,7 +1294,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1335,19 +1335,19 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1371,19 +1371,19 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1394,7 +1394,7 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1403,7 +1403,7 @@
         <v>8</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -1412,7 +1412,7 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>8</v>
@@ -1421,10 +1421,10 @@
         <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1448,7 +1448,7 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1457,10 +1457,10 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1489,7 +1489,7 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -1498,10 +1498,10 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1537,7 +1537,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1566,7 +1566,7 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -1575,10 +1575,10 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1602,7 +1602,7 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1611,7 +1611,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>10</v>
@@ -1652,10 +1652,10 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1679,7 +1679,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1691,7 +1691,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1720,7 +1720,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>9</v>
@@ -1729,10 +1729,10 @@
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1756,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1765,7 +1765,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1797,19 +1797,19 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1833,13 +1833,13 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1874,19 +1874,19 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1910,19 +1910,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1951,7 +1951,7 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>9</v>
@@ -1960,10 +1960,10 @@
         <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1999,7 +1999,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2010,7 +2010,7 @@
         <v>9</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -2028,7 +2028,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>8</v>
@@ -2037,10 +2037,10 @@
         <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2064,7 +2064,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2073,7 +2073,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2087,7 +2087,7 @@
         <v>10</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2105,19 +2105,19 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2141,13 +2141,13 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>8</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2182,7 +2182,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -2191,10 +2191,10 @@
         <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2218,7 +2218,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2259,19 +2259,19 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2295,19 +2295,19 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2318,7 +2318,7 @@
         <v>10</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>9</v>
@@ -2336,7 +2336,7 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>8</v>
@@ -2345,10 +2345,10 @@
         <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2372,7 +2372,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2381,10 +2381,10 @@
         <v>10</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2413,7 +2413,7 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>8</v>
@@ -2422,10 +2422,10 @@
         <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2458,7 +2458,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2490,7 +2490,7 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>6</v>
@@ -2499,10 +2499,10 @@
         <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2567,7 +2567,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>9</v>
@@ -2576,10 +2576,10 @@
         <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2626,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -2635,7 +2635,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <v>8</v>
@@ -2644,7 +2644,7 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>8</v>
@@ -2653,10 +2653,10 @@
         <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2680,7 +2680,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>7</v>
@@ -2689,7 +2689,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2721,19 +2721,19 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2757,19 +2757,19 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>8</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2780,7 +2780,7 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -2789,7 +2789,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>8</v>
@@ -2798,7 +2798,7 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -2807,10 +2807,10 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2834,7 +2834,7 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>6</v>
@@ -2843,7 +2843,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2875,7 +2875,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -2884,10 +2884,10 @@
         <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2920,10 +2920,10 @@
         <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2952,7 +2952,7 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>10</v>
@@ -2961,10 +2961,10 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3000,7 +3000,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3029,19 +3029,19 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3065,13 +3065,13 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>8</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -3106,19 +3106,19 @@
         <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3151,10 +3151,10 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3183,7 +3183,7 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>9</v>
@@ -3192,10 +3192,10 @@
         <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3231,7 +3231,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3260,19 +3260,19 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3302,13 +3302,13 @@
         <v>8</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3337,7 +3337,7 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
         <v>9</v>
@@ -3346,10 +3346,10 @@
         <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3450,25 +3450,25 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>81.25</v>
+        <v>78.13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>21.88</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3482,25 +3482,25 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>90.63</v>
+        <v>87.5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3526,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3638,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3663,186 +3663,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920156</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920156</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920164</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920166</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920169</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920175</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920175</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920177</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920177</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3878,115 +3698,115 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920156</v>
+        <v>21330051920151</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920175</v>
+        <v>21330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920177</v>
+        <v>21330051920153</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920164</v>
+        <v>21330051920154</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920166</v>
+        <v>21330051920155</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920169</v>
+        <v>21330051920156</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920151</v>
+        <v>21330051920157</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
         <v>118</v>
@@ -3997,13 +3817,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920152</v>
+        <v>21330051920158</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
         <v>119</v>
@@ -4014,13 +3834,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920153</v>
+        <v>21330051920159</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
         <v>120</v>
@@ -4031,13 +3851,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920154</v>
+        <v>21330051920160</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
         <v>121</v>
@@ -4048,13 +3868,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920155</v>
+        <v>21330051920161</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
         <v>122</v>
@@ -4065,13 +3885,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920157</v>
+        <v>21330051920162</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>123</v>
@@ -4082,13 +3902,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920158</v>
+        <v>21330051920163</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
         <v>124</v>
@@ -4099,13 +3919,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920159</v>
+        <v>21330051920164</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
         <v>125</v>
@@ -4116,13 +3936,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920160</v>
+        <v>21330051920165</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
         <v>126</v>
@@ -4133,13 +3953,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920161</v>
+        <v>21330051920166</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
         <v>127</v>
@@ -4150,13 +3970,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920162</v>
+        <v>21330051920167</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
         <v>128</v>
@@ -4167,13 +3987,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920163</v>
+        <v>21330051920168</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
         <v>129</v>
@@ -4184,13 +4004,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920165</v>
+        <v>21330051920169</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
         <v>130</v>
@@ -4201,13 +4021,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920167</v>
+        <v>21330051920170</v>
       </c>
       <c r="B21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" t="s">
         <v>91</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
       </c>
       <c r="D21" t="s">
         <v>131</v>
@@ -4218,13 +4038,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920168</v>
+        <v>21330051920171</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
         <v>132</v>
@@ -4235,13 +4055,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920170</v>
+        <v>21330051920173</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
         <v>133</v>
@@ -4252,13 +4072,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920171</v>
+        <v>21330051920175</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>134</v>
@@ -4269,13 +4089,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920173</v>
+        <v>21330051920176</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
         <v>135</v>
@@ -4286,13 +4106,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920176</v>
+        <v>21330051920177</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
         <v>136</v>
@@ -4306,10 +4126,10 @@
         <v>21330051920178</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
         <v>137</v>
@@ -4323,10 +4143,10 @@
         <v>21330051920179</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>138</v>
@@ -4340,10 +4160,10 @@
         <v>21330051920180</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
         <v>139</v>
@@ -4357,10 +4177,10 @@
         <v>21330051920181</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
         <v>140</v>
@@ -4374,10 +4194,10 @@
         <v>21330051920182</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
         <v>141</v>
@@ -4391,13 +4211,13 @@
         <v>21330051920183</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4408,13 +4228,13 @@
         <v>21330051920184</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -4427,7 +4247,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4462,13 +4282,13 @@
         <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4477,7 +4297,7 @@
         <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4485,13 +4305,13 @@
         <v>21330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4500,21 +4320,21 @@
         <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920175</v>
+        <v>21330051920164</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4523,21 +4343,21 @@
         <v>53</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920175</v>
+        <v>21330051920164</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -4546,21 +4366,21 @@
         <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920177</v>
+        <v>21330051920175</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4569,21 +4389,21 @@
         <v>53</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920177</v>
+        <v>21330051920175</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -4592,21 +4412,21 @@
         <v>54</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920164</v>
+        <v>21330051920177</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4615,44 +4435,44 @@
         <v>53</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920166</v>
+        <v>21330051920177</v>
       </c>
       <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
         <v>65</v>
       </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920169</v>
+        <v>21330051920162</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4661,7 +4481,53 @@
         <v>53</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920166</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920168</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2AEM - Estadisticos 20212.xlsx
+++ b/grupos/2AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="142">
   <si>
     <t>Materia</t>
   </si>
@@ -179,16 +179,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
@@ -965,22 +965,22 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1042,28 +1042,28 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1119,28 +1119,28 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>9</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1152,7 +1152,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1196,22 +1196,22 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1226,7 +1226,7 @@
         <v>9</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1273,22 +1273,22 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1303,7 +1303,7 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1350,22 +1350,22 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1427,37 +1427,37 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>7</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1504,22 +1504,22 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1581,22 +1581,22 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1608,10 +1608,10 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1658,22 +1658,22 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1735,22 +1735,22 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1812,34 +1812,34 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1889,22 +1889,22 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1919,10 +1919,10 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1966,22 +1966,22 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2043,28 +2043,28 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>10</v>
       </c>
       <c r="U18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2073,7 +2073,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2120,28 +2120,28 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>10</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2197,22 +2197,22 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2274,37 +2274,37 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>9</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2351,22 +2351,22 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2381,7 +2381,7 @@
         <v>10</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2428,37 +2428,37 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>9</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2505,28 +2505,28 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>10</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2535,7 +2535,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2582,22 +2582,22 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2659,28 +2659,28 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>10</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>7</v>
@@ -2689,7 +2689,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2736,28 +2736,28 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>10</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -2766,7 +2766,7 @@
         <v>8</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2813,37 +2813,37 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>6</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2890,22 +2890,22 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2967,22 +2967,22 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -3044,34 +3044,34 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>8</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -3121,22 +3121,22 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3198,22 +3198,22 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3228,7 +3228,7 @@
         <v>9</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3275,22 +3275,22 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3305,7 +3305,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3352,28 +3352,28 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>9</v>
@@ -3382,7 +3382,7 @@
         <v>10</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3450,19 +3450,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3482,19 +3482,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3526,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3537,7 +3537,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3558,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4247,7 +4247,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4277,259 +4277,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920156</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920156</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920164</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920164</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920175</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920175</v>
-      </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920177</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920177</v>
-      </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920162</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920166</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920168</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2AEM - Estadisticos 20212.xlsx
+++ b/grupos/2AEM - Estadisticos 20212.xlsx
@@ -971,7 +971,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -989,7 +989,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>9</v>
@@ -1048,7 +1048,7 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1125,7 +1125,7 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1202,7 +1202,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>9</v>
@@ -1279,7 +1279,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1297,7 +1297,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1356,7 +1356,7 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>8</v>
@@ -1374,7 +1374,7 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1433,7 +1433,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1510,7 +1510,7 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1528,7 +1528,7 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1587,7 +1587,7 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>7</v>
@@ -1605,7 +1605,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1664,7 +1664,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1741,7 +1741,7 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1759,7 +1759,7 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1818,7 +1818,7 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>6</v>
@@ -1895,7 +1895,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -1913,7 +1913,7 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1972,7 +1972,7 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -1990,7 +1990,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2049,7 +2049,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>8</v>
@@ -2067,7 +2067,7 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2126,7 +2126,7 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2144,7 +2144,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2203,7 +2203,7 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2221,7 +2221,7 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2280,7 +2280,7 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>7</v>
@@ -2298,7 +2298,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2357,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2375,7 +2375,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2434,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2452,7 +2452,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2511,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2529,7 +2529,7 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2588,7 +2588,7 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2606,7 +2606,7 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2665,7 +2665,7 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2742,7 +2742,7 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>10</v>
@@ -2760,7 +2760,7 @@
         <v>6</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2819,7 +2819,7 @@
         <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2896,7 +2896,7 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -2973,7 +2973,7 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3050,7 +3050,7 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3127,7 +3127,7 @@
         <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -3204,7 +3204,7 @@
         <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3222,7 +3222,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3281,7 +3281,7 @@
         <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3358,7 +3358,7 @@
         <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -3376,7 +3376,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3526,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
